--- a/tests/fixtures/corpus/pivot_slicer.xlsx
+++ b/tests/fixtures/corpus/pivot_slicer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCF2BBA1-E9D7-4CDA-A427-639305FC2C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71011789-99BE-4F97-9BA5-50D6C2F046BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" xr2:uid="{BE7E23F4-0B64-4892-8DBB-2D915946AA2F}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="16200" windowHeight="9307" xr2:uid="{46538A04-5392-437D-AA98-F984897C10F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Pvt" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
             <xdr:cNvPr id="2" name="Region">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C293766-729F-435F-75D8-1B2C2F345E7A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7E95D82-33D9-3698-2AF7-AC5D48795DA6}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Zeta" refreshedDate="46268.216120023149" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{D26257EB-5868-4BB4-8257-6A10DD91A407}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Zeta" refreshedDate="46269.758384606481" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{BDC56364-2AA2-4E7F-BEFC-57CCADAD8D02}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:C7" sheet="Src"/>
   </cacheSource>
@@ -250,7 +250,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1291265881"/>
+      <x14:pivotCacheDefinition pivotCacheId="634912260"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -292,7 +292,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{083D2807-4AE7-4D5C-B71D-4D59210DF2E0}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A95CFD15-0F3B-4788-9E4A-321A197C65B4}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -344,12 +344,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{98A521A1-8157-482D-B8B3-8E7FA87567D5}" sourceName="Region">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{9AC3238B-48E9-4C54-8E81-59971D2E0C26}" sourceName="Region">
   <pivotTables>
     <pivotTable tabId="2" name="PivotTable1"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1291265881">
+    <tabular pivotCacheId="634912260">
       <items count="2">
         <i x="0" s="1"/>
         <i x="1" s="1"/>
@@ -361,7 +361,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Region" xr10:uid="{FC78F0D4-7902-4723-B718-D24FFB2DC6F8}" cache="Slicer_Region" caption="Region" rowHeight="233363"/>
+  <slicer name="Region" xr10:uid="{5707AE1C-D7AD-4A63-A28D-C4890DD54CBB}" cache="Slicer_Region" caption="Region" rowHeight="233363"/>
 </slicers>
 </file>
 
@@ -681,7 +681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9BCCA6-B147-4F46-A638-AF4A1EBC71D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8F8B09-D71D-45DB-A645-547DD0E161FE}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -735,7 +735,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76EB8860-483B-4F1D-9AFE-CF2084EAF959}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{879C9631-C215-4B95-9D0B-6328BD9E8DA2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
